--- a/sheet-template/GAMEOVER_시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_시트_261012.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>동명대학교 (강의실 확정 후 공지)</t>
+          <t>동명대학교 대학본관 107호</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>동명대학교</t>
+          <t>동명대학교 대학본관 107호</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>강의실은 확정되면 이 페이지에 올립니다.
+          <t>대학본관(1번 건물) 107호에서 진행합니다.
 부산 · 울산 지역에서 오시는 분들을 위한 안내도 함께 올리겠습니다.</t>
         </is>
       </c>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>토요일 개최입니다. 건물 출입 안내는 확정 후 공지합니다.</t>
+          <t>토요일 개최입니다. 건물 출입 안내는 확정되는 대로 공지합니다.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
